--- a/public/samples/de/sample1.xlsx
+++ b/public/samples/de/sample1.xlsx
@@ -35,7 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -77,10 +79,11 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,7 +498,7 @@
         <v>DaZ</v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>Verhalten</v>
+        <v>Unterstützung Verhalten</v>
       </c>
       <c r="H2" s="2" t="str">
         <v>Herkunftsgrundschule</v>
@@ -511,7 +514,7 @@
       <c r="C3" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>2.6</v>
       </c>
       <c r="E3" s="2" t="str">
@@ -521,7 +524,7 @@
         <v/>
       </c>
       <c r="G3" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H3" s="2" t="str">
         <v>GS Am Park</v>
@@ -537,7 +540,7 @@
       <c r="C4" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>2.4</v>
       </c>
       <c r="E4" s="2" t="str">
@@ -547,7 +550,7 @@
         <v/>
       </c>
       <c r="G4" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H4" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -563,7 +566,7 @@
       <c r="C5" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>2.2</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -573,7 +576,7 @@
         <v/>
       </c>
       <c r="G5" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H5" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -589,7 +592,7 @@
       <c r="C6" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>2.5</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -599,7 +602,7 @@
         <v/>
       </c>
       <c r="G6" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H6" s="2" t="str">
         <v>GS Am Park</v>
@@ -615,7 +618,7 @@
       <c r="C7" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>2.8</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -625,7 +628,7 @@
         <v/>
       </c>
       <c r="G7" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H7" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -641,7 +644,7 @@
       <c r="C8" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>2.9</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -651,7 +654,7 @@
         <v/>
       </c>
       <c r="G8" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H8" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -667,7 +670,7 @@
       <c r="C9" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>2.6</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -677,7 +680,7 @@
         <v/>
       </c>
       <c r="G9" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H9" s="2" t="str">
         <v>GS Am Park</v>
@@ -693,7 +696,7 @@
       <c r="C10" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>2.9</v>
       </c>
       <c r="E10" s="2" t="str">
@@ -703,7 +706,7 @@
         <v/>
       </c>
       <c r="G10" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H10" s="2" t="str">
         <v>GS Am Park</v>
@@ -719,7 +722,7 @@
       <c r="C11" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>2.6</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -729,7 +732,7 @@
         <v/>
       </c>
       <c r="G11" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H11" s="2" t="str">
         <v>GS Nord</v>
@@ -745,8 +748,8 @@
       <c r="C12" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D12" s="2" t="str">
-        <v>3.0</v>
+      <c r="D12" s="3">
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="str">
         <v/>
@@ -755,7 +758,7 @@
         <v/>
       </c>
       <c r="G12" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H12" s="2" t="str">
         <v>GS Am Park</v>
@@ -771,7 +774,7 @@
       <c r="C13" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>2.7</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -781,7 +784,7 @@
         <v/>
       </c>
       <c r="G13" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H13" s="2" t="str">
         <v>GS Nord</v>
@@ -797,7 +800,7 @@
       <c r="C14" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>1.7</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -807,7 +810,7 @@
         <v>✓</v>
       </c>
       <c r="G14" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H14" s="2" t="str">
         <v>GS Nord</v>
@@ -823,7 +826,7 @@
       <c r="C15" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>2.2</v>
       </c>
       <c r="E15" s="2" t="str">
@@ -833,7 +836,7 @@
         <v>✓</v>
       </c>
       <c r="G15" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H15" s="2" t="str">
         <v>GS Nord</v>
@@ -849,7 +852,7 @@
       <c r="C16" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>1.4</v>
       </c>
       <c r="E16" s="2" t="str">
@@ -859,7 +862,7 @@
         <v/>
       </c>
       <c r="G16" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H16" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -875,7 +878,7 @@
       <c r="C17" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>3.3</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -885,7 +888,7 @@
         <v>✓</v>
       </c>
       <c r="G17" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H17" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -901,7 +904,7 @@
       <c r="C18" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>2.6</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -911,7 +914,7 @@
         <v/>
       </c>
       <c r="G18" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H18" s="2" t="str">
         <v>GS Süd</v>
@@ -927,7 +930,7 @@
       <c r="C19" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>3.2</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -937,7 +940,7 @@
         <v/>
       </c>
       <c r="G19" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H19" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -953,7 +956,7 @@
       <c r="C20" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>3.3</v>
       </c>
       <c r="E20" s="2" t="str">
@@ -963,7 +966,7 @@
         <v/>
       </c>
       <c r="G20" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H20" s="2" t="str">
         <v>GS Nord</v>
@@ -979,7 +982,7 @@
       <c r="C21" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>2.3</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -989,7 +992,7 @@
         <v/>
       </c>
       <c r="G21" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H21" s="2" t="str">
         <v>GS Süd</v>
@@ -1005,7 +1008,7 @@
       <c r="C22" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>3.6</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -1015,7 +1018,7 @@
         <v/>
       </c>
       <c r="G22" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H22" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1031,7 +1034,7 @@
       <c r="C23" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>2.2</v>
       </c>
       <c r="E23" s="2" t="str">
@@ -1041,7 +1044,7 @@
         <v/>
       </c>
       <c r="G23" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H23" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1057,8 +1060,8 @@
       <c r="C24" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D24" s="2" t="str">
-        <v>2.0</v>
+      <c r="D24" s="3">
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="str">
         <v/>
@@ -1067,7 +1070,7 @@
         <v/>
       </c>
       <c r="G24" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H24" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1083,7 +1086,7 @@
       <c r="C25" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>2.2</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -1093,7 +1096,7 @@
         <v/>
       </c>
       <c r="G25" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H25" s="2" t="str">
         <v>GS Nord</v>
@@ -1109,7 +1112,7 @@
       <c r="C26" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>2.4</v>
       </c>
       <c r="E26" s="2" t="str">
@@ -1119,7 +1122,7 @@
         <v/>
       </c>
       <c r="G26" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H26" s="2" t="str">
         <v>GS Am Park</v>
@@ -1135,7 +1138,7 @@
       <c r="C27" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>2.7</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -1145,7 +1148,7 @@
         <v/>
       </c>
       <c r="G27" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H27" s="2" t="str">
         <v>GS Am Park</v>
@@ -1161,7 +1164,7 @@
       <c r="C28" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>2.5</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -1171,7 +1174,7 @@
         <v/>
       </c>
       <c r="G28" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H28" s="2" t="str">
         <v>GS Nord</v>
@@ -1187,7 +1190,7 @@
       <c r="C29" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>2.5</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -1197,7 +1200,7 @@
         <v/>
       </c>
       <c r="G29" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H29" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1213,7 +1216,7 @@
       <c r="C30" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>2.6</v>
       </c>
       <c r="E30" s="2" t="str">
@@ -1223,7 +1226,7 @@
         <v/>
       </c>
       <c r="G30" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H30" s="2" t="str">
         <v>GS Nord</v>
@@ -1239,8 +1242,8 @@
       <c r="C31" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D31" s="2" t="str">
-        <v>2.0</v>
+      <c r="D31" s="3">
+        <v>2</v>
       </c>
       <c r="E31" s="2" t="str">
         <v/>
@@ -1249,7 +1252,7 @@
         <v/>
       </c>
       <c r="G31" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H31" s="2" t="str">
         <v>GS Süd</v>
@@ -1265,8 +1268,8 @@
       <c r="C32" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D32" s="2" t="str">
-        <v>3.0</v>
+      <c r="D32" s="3">
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="str">
         <v/>
@@ -1275,7 +1278,7 @@
         <v>✓</v>
       </c>
       <c r="G32" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H32" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1291,7 +1294,7 @@
       <c r="C33" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="3">
         <v>1.8</v>
       </c>
       <c r="E33" s="2" t="str">
@@ -1301,7 +1304,7 @@
         <v>✓</v>
       </c>
       <c r="G33" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H33" s="2" t="str">
         <v>GS Am Park</v>
@@ -1317,7 +1320,7 @@
       <c r="C34" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>1.9</v>
       </c>
       <c r="E34" s="2" t="str">
@@ -1327,7 +1330,7 @@
         <v/>
       </c>
       <c r="G34" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H34" s="2" t="str">
         <v>GS Süd</v>
@@ -1343,8 +1346,8 @@
       <c r="C35" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D35" s="2" t="str">
-        <v>2.0</v>
+      <c r="D35" s="3">
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="str">
         <v/>
@@ -1353,7 +1356,7 @@
         <v/>
       </c>
       <c r="G35" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H35" s="2" t="str">
         <v>GS Nord</v>
@@ -1369,7 +1372,7 @@
       <c r="C36" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
         <v>2.2</v>
       </c>
       <c r="E36" s="2" t="str">
@@ -1379,7 +1382,7 @@
         <v/>
       </c>
       <c r="G36" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H36" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1395,7 +1398,7 @@
       <c r="C37" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>2.5</v>
       </c>
       <c r="E37" s="2" t="str">
@@ -1405,7 +1408,7 @@
         <v/>
       </c>
       <c r="G37" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H37" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1421,7 +1424,7 @@
       <c r="C38" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
         <v>2.9</v>
       </c>
       <c r="E38" s="2" t="str">
@@ -1431,7 +1434,7 @@
         <v/>
       </c>
       <c r="G38" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H38" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1447,7 +1450,7 @@
       <c r="C39" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>2.5</v>
       </c>
       <c r="E39" s="2" t="str">
@@ -1457,7 +1460,7 @@
         <v/>
       </c>
       <c r="G39" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H39" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1473,7 +1476,7 @@
       <c r="C40" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="3">
         <v>2.2</v>
       </c>
       <c r="E40" s="2" t="str">
@@ -1483,7 +1486,7 @@
         <v/>
       </c>
       <c r="G40" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H40" s="2" t="str">
         <v>GS Süd</v>
@@ -1499,7 +1502,7 @@
       <c r="C41" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>1.9</v>
       </c>
       <c r="E41" s="2" t="str">
@@ -1509,7 +1512,7 @@
         <v>✓</v>
       </c>
       <c r="G41" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H41" s="2" t="str">
         <v>GS Am Park</v>
@@ -1525,7 +1528,7 @@
       <c r="C42" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>2.2</v>
       </c>
       <c r="E42" s="2" t="str">
@@ -1535,7 +1538,7 @@
         <v/>
       </c>
       <c r="G42" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H42" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1551,7 +1554,7 @@
       <c r="C43" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>1.9</v>
       </c>
       <c r="E43" s="2" t="str">
@@ -1561,7 +1564,7 @@
         <v/>
       </c>
       <c r="G43" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H43" s="2" t="str">
         <v>GS Am Park</v>
@@ -1577,7 +1580,7 @@
       <c r="C44" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>2.9</v>
       </c>
       <c r="E44" s="2" t="str">
@@ -1587,7 +1590,7 @@
         <v/>
       </c>
       <c r="G44" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H44" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1603,7 +1606,7 @@
       <c r="C45" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>2.3</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -1613,7 +1616,7 @@
         <v/>
       </c>
       <c r="G45" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H45" s="2" t="str">
         <v>GS Süd</v>
@@ -1629,7 +1632,7 @@
       <c r="C46" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
         <v>2.6</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -1639,7 +1642,7 @@
         <v/>
       </c>
       <c r="G46" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H46" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1655,7 +1658,7 @@
       <c r="C47" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>1.7</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -1665,7 +1668,7 @@
         <v>✓</v>
       </c>
       <c r="G47" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H47" s="2" t="str">
         <v>GS Nord</v>
@@ -1681,7 +1684,7 @@
       <c r="C48" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>2.2</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -1691,7 +1694,7 @@
         <v/>
       </c>
       <c r="G48" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H48" s="2" t="str">
         <v>GS Nord</v>
@@ -1707,7 +1710,7 @@
       <c r="C49" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>2.8</v>
       </c>
       <c r="E49" s="2" t="str">
@@ -1717,7 +1720,7 @@
         <v/>
       </c>
       <c r="G49" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H49" s="2" t="str">
         <v>GS Nord</v>
@@ -1733,7 +1736,7 @@
       <c r="C50" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
         <v>2.3</v>
       </c>
       <c r="E50" s="2" t="str">
@@ -1743,7 +1746,7 @@
         <v/>
       </c>
       <c r="G50" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H50" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1759,7 +1762,7 @@
       <c r="C51" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <v>2.7</v>
       </c>
       <c r="E51" s="2" t="str">
@@ -1769,7 +1772,7 @@
         <v/>
       </c>
       <c r="G51" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H51" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1785,7 +1788,7 @@
       <c r="C52" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <v>2.6</v>
       </c>
       <c r="E52" s="2" t="str">
@@ -1795,7 +1798,7 @@
         <v/>
       </c>
       <c r="G52" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H52" s="2" t="str">
         <v>GS Am Park</v>
@@ -1811,8 +1814,8 @@
       <c r="C53" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D53" s="2" t="str">
-        <v>3.0</v>
+      <c r="D53" s="3">
+        <v>3</v>
       </c>
       <c r="E53" s="2" t="str">
         <v/>
@@ -1821,7 +1824,7 @@
         <v/>
       </c>
       <c r="G53" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H53" s="2" t="str">
         <v>GS Am Park</v>
@@ -1837,7 +1840,7 @@
       <c r="C54" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
         <v>2.3</v>
       </c>
       <c r="E54" s="2" t="str">
@@ -1847,7 +1850,7 @@
         <v/>
       </c>
       <c r="G54" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H54" s="2" t="str">
         <v>GS Süd</v>
@@ -1863,7 +1866,7 @@
       <c r="C55" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="3">
         <v>2.6</v>
       </c>
       <c r="E55" s="2" t="str">
@@ -1873,7 +1876,7 @@
         <v/>
       </c>
       <c r="G55" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H55" s="2" t="str">
         <v>GS Nord</v>
@@ -1889,7 +1892,7 @@
       <c r="C56" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="3">
         <v>2.9</v>
       </c>
       <c r="E56" s="2" t="str">
@@ -1899,7 +1902,7 @@
         <v/>
       </c>
       <c r="G56" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H56" s="2" t="str">
         <v>GS Am Park</v>
@@ -1915,7 +1918,7 @@
       <c r="C57" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
         <v>2.9</v>
       </c>
       <c r="E57" s="2" t="str">
@@ -1925,7 +1928,7 @@
         <v/>
       </c>
       <c r="G57" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H57" s="2" t="str">
         <v>GS Nord</v>
@@ -1941,7 +1944,7 @@
       <c r="C58" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="3">
         <v>2.4</v>
       </c>
       <c r="E58" s="2" t="str">
@@ -1951,7 +1954,7 @@
         <v/>
       </c>
       <c r="G58" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H58" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -1967,7 +1970,7 @@
       <c r="C59" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
         <v>1.8</v>
       </c>
       <c r="E59" s="2" t="str">
@@ -1977,7 +1980,7 @@
         <v/>
       </c>
       <c r="G59" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H59" s="2" t="str">
         <v>GS Süd</v>
@@ -1993,7 +1996,7 @@
       <c r="C60" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="3">
         <v>1.7</v>
       </c>
       <c r="E60" s="2" t="str">
@@ -2003,7 +2006,7 @@
         <v/>
       </c>
       <c r="G60" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H60" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2019,7 +2022,7 @@
       <c r="C61" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="3">
         <v>2.2</v>
       </c>
       <c r="E61" s="2" t="str">
@@ -2029,7 +2032,7 @@
         <v/>
       </c>
       <c r="G61" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H61" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2045,8 +2048,8 @@
       <c r="C62" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D62" s="2" t="str">
-        <v>3.0</v>
+      <c r="D62" s="3">
+        <v>3</v>
       </c>
       <c r="E62" s="2" t="str">
         <v/>
@@ -2055,7 +2058,7 @@
         <v/>
       </c>
       <c r="G62" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H62" s="2" t="str">
         <v>GS Nord</v>
@@ -2071,7 +2074,7 @@
       <c r="C63" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="3">
         <v>2.5</v>
       </c>
       <c r="E63" s="2" t="str">
@@ -2081,7 +2084,7 @@
         <v/>
       </c>
       <c r="G63" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H63" s="2" t="str">
         <v>GS Süd</v>
@@ -2097,7 +2100,7 @@
       <c r="C64" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="3">
         <v>2.6</v>
       </c>
       <c r="E64" s="2" t="str">
@@ -2107,7 +2110,7 @@
         <v/>
       </c>
       <c r="G64" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H64" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2123,7 +2126,7 @@
       <c r="C65" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="3">
         <v>2.3</v>
       </c>
       <c r="E65" s="2" t="str">
@@ -2133,7 +2136,7 @@
         <v/>
       </c>
       <c r="G65" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H65" s="2" t="str">
         <v>GS Süd</v>
@@ -2149,7 +2152,7 @@
       <c r="C66" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="3">
         <v>2.6</v>
       </c>
       <c r="E66" s="2" t="str">
@@ -2159,7 +2162,7 @@
         <v/>
       </c>
       <c r="G66" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H66" s="2" t="str">
         <v>GS Am Park</v>
@@ -2175,7 +2178,7 @@
       <c r="C67" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="3">
         <v>1.6</v>
       </c>
       <c r="E67" s="2" t="str">
@@ -2185,7 +2188,7 @@
         <v/>
       </c>
       <c r="G67" s="2" t="str">
-        <v>Unterstützung</v>
+        <v/>
       </c>
       <c r="H67" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2201,7 +2204,7 @@
       <c r="C68" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="3">
         <v>1.8</v>
       </c>
       <c r="E68" s="2" t="str">
@@ -2211,7 +2214,7 @@
         <v/>
       </c>
       <c r="G68" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H68" s="2" t="str">
         <v>GS Am Park</v>
@@ -2227,7 +2230,7 @@
       <c r="C69" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="3">
         <v>3.6</v>
       </c>
       <c r="E69" s="2" t="str">
@@ -2237,7 +2240,7 @@
         <v/>
       </c>
       <c r="G69" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H69" s="2" t="str">
         <v>GS Süd</v>
@@ -2253,8 +2256,8 @@
       <c r="C70" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D70" s="2" t="str">
-        <v>3.0</v>
+      <c r="D70" s="3">
+        <v>3</v>
       </c>
       <c r="E70" s="2" t="str">
         <v>✓</v>
@@ -2263,7 +2266,7 @@
         <v/>
       </c>
       <c r="G70" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H70" s="2" t="str">
         <v>GS Am Park</v>
@@ -2279,7 +2282,7 @@
       <c r="C71" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="3">
         <v>2.5</v>
       </c>
       <c r="E71" s="2" t="str">
@@ -2289,7 +2292,7 @@
         <v/>
       </c>
       <c r="G71" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H71" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2305,7 +2308,7 @@
       <c r="C72" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="3">
         <v>2.6</v>
       </c>
       <c r="E72" s="2" t="str">
@@ -2315,7 +2318,7 @@
         <v/>
       </c>
       <c r="G72" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H72" s="2" t="str">
         <v>GS Am Park</v>
@@ -2331,7 +2334,7 @@
       <c r="C73" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="3">
         <v>3.3</v>
       </c>
       <c r="E73" s="2" t="str">
@@ -2341,7 +2344,7 @@
         <v>✓</v>
       </c>
       <c r="G73" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H73" s="2" t="str">
         <v>GS Süd</v>
@@ -2357,7 +2360,7 @@
       <c r="C74" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="3">
         <v>2.5</v>
       </c>
       <c r="E74" s="2" t="str">
@@ -2367,7 +2370,7 @@
         <v/>
       </c>
       <c r="G74" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H74" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2383,7 +2386,7 @@
       <c r="C75" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="3">
         <v>2.8</v>
       </c>
       <c r="E75" s="2" t="str">
@@ -2393,7 +2396,7 @@
         <v/>
       </c>
       <c r="G75" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H75" s="2" t="str">
         <v>GS Süd</v>
@@ -2409,7 +2412,7 @@
       <c r="C76" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="3">
         <v>2.3</v>
       </c>
       <c r="E76" s="2" t="str">
@@ -2419,7 +2422,7 @@
         <v/>
       </c>
       <c r="G76" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H76" s="2" t="str">
         <v>GS Am Park</v>
@@ -2435,7 +2438,7 @@
       <c r="C77" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="3">
         <v>3.6</v>
       </c>
       <c r="E77" s="2" t="str">
@@ -2445,7 +2448,7 @@
         <v/>
       </c>
       <c r="G77" s="2" t="str">
-        <v>unauffällig</v>
+        <v>✓</v>
       </c>
       <c r="H77" s="2" t="str">
         <v>GS Am Park</v>
@@ -2461,7 +2464,7 @@
       <c r="C78" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="3">
         <v>3.2</v>
       </c>
       <c r="E78" s="2" t="str">
@@ -2471,7 +2474,7 @@
         <v/>
       </c>
       <c r="G78" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H78" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2487,7 +2490,7 @@
       <c r="C79" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="3">
         <v>2.5</v>
       </c>
       <c r="E79" s="2" t="str">
@@ -2497,7 +2500,7 @@
         <v/>
       </c>
       <c r="G79" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H79" s="2" t="str">
         <v>GS Lindenweg</v>
@@ -2513,7 +2516,7 @@
       <c r="C80" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="3">
         <v>1.9</v>
       </c>
       <c r="E80" s="2" t="str">
@@ -2523,7 +2526,7 @@
         <v/>
       </c>
       <c r="G80" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H80" s="2" t="str">
         <v>GS Süd</v>
@@ -2539,7 +2542,7 @@
       <c r="C81" s="2" t="str">
         <v>w</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="3">
         <v>2.6</v>
       </c>
       <c r="E81" s="2" t="str">
@@ -2549,7 +2552,7 @@
         <v>✓</v>
       </c>
       <c r="G81" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H81" s="2" t="str">
         <v>GS Am Park</v>
@@ -2565,7 +2568,7 @@
       <c r="C82" s="2" t="str">
         <v>m</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="3">
         <v>2.6</v>
       </c>
       <c r="E82" s="2" t="str">
@@ -2575,7 +2578,7 @@
         <v>✓</v>
       </c>
       <c r="G82" s="2" t="str">
-        <v>unauffällig</v>
+        <v/>
       </c>
       <c r="H82" s="2" t="str">
         <v>GS Lindenweg</v>

--- a/public/samples/de/sample1.xlsx
+++ b/public/samples/de/sample1.xlsx
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:I82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -477,6 +477,9 @@
       <c r="H1" s="2">
         <v>1</v>
       </c>
+      <c r="I1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -492,15 +495,18 @@
         <v>Notenschnitt</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>Förderbedarf</v>
+        <v>Lesekompetenz</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Förderung</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>DaZ</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <v>Unterstützung Verhalten</v>
-      </c>
       <c r="H2" s="2" t="str">
+        <v>Teamfähigkeit</v>
+      </c>
+      <c r="I2" s="2" t="str">
         <v>Herkunftsgrundschule</v>
       </c>
     </row>
@@ -517,8 +523,8 @@
       <c r="D3" s="3">
         <v>2.6</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
         <v/>
@@ -527,7 +533,10 @@
         <v/>
       </c>
       <c r="H3" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I3" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="4">
@@ -535,25 +544,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Noah Schmidt</v>
+        <v>Noah Fischer</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D4" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="E4" s="2" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H4" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H4" s="2" t="str">
-        <v>GS Lindenweg</v>
+      <c r="I4" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +573,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Mia Hoffmann</v>
+        <v>Mia Fischer</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D5" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="str">
         <v/>
@@ -579,7 +591,10 @@
         <v/>
       </c>
       <c r="H5" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +602,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Leon Schröder</v>
+        <v>Leon Hoffmann</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D6" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="str">
         <v/>
@@ -605,7 +620,10 @@
         <v/>
       </c>
       <c r="H6" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I6" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="7">
@@ -613,16 +631,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Sophia Richter</v>
+        <v>Sophia Klein</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D7" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>2.1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
         <v/>
@@ -631,6 +649,9 @@
         <v/>
       </c>
       <c r="H7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I7" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -639,25 +660,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Paul Hartmann</v>
+        <v>Paul Wagner</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>m</v>
+        <v>d</v>
       </c>
       <c r="D8" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="str">
         <v/>
       </c>
       <c r="G8" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H8" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I8" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="9">
@@ -665,16 +689,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Hannah Richter</v>
+        <v>Hannah Fischer</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D9" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="str">
         <v/>
@@ -683,7 +707,10 @@
         <v/>
       </c>
       <c r="H9" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I9" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="10">
@@ -691,16 +718,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Ben Müller</v>
+        <v>Ben Hartmann</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D10" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="str">
         <v/>
@@ -709,7 +736,10 @@
         <v/>
       </c>
       <c r="H10" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I10" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="11">
@@ -717,16 +747,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Lina Hartmann</v>
+        <v>Lina Klein</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D11" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="str">
         <v/>
@@ -735,7 +765,10 @@
         <v/>
       </c>
       <c r="H11" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I11" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +776,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Finn Zimmermann</v>
+        <v>Finn Fischer</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>m</v>
@@ -751,8 +784,8 @@
       <c r="D12" s="3">
         <v>3</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
         <v/>
@@ -761,7 +794,10 @@
         <v/>
       </c>
       <c r="H12" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I12" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="13">
@@ -769,16 +805,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Emma Krüger</v>
+        <v>Emma Neumann</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D13" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>1.7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
         <v/>
@@ -787,7 +823,10 @@
         <v/>
       </c>
       <c r="H13" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I13" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +834,28 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Elias Neumann</v>
+        <v>Elias Wolf</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D14" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H14" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="G14" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H14" s="2" t="str">
-        <v>GS Nord</v>
+      <c r="I14" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="15">
@@ -821,25 +863,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Mila Braun</v>
+        <v>Mila Schmidt</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D15" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v>✓</v>
+        <v>2.4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G15" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H15" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I15" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="16">
@@ -847,16 +892,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Felix Meyer</v>
+        <v>Felix Schröder</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D16" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
         <v/>
@@ -865,7 +910,10 @@
         <v/>
       </c>
       <c r="H16" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="17">
@@ -873,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Clara Koch</v>
+        <v>Clara Schulz</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>w</v>
@@ -881,17 +929,20 @@
       <c r="D17" s="3">
         <v>3.3</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+      <c r="E17" s="2">
+        <v>4</v>
       </c>
       <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="G17" s="2" t="str">
-        <v/>
-      </c>
       <c r="H17" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I17" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="18">
@@ -899,16 +950,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Henry Richter</v>
+        <v>Henry Hoffmann</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D18" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>3.1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="str">
         <v/>
@@ -917,7 +968,10 @@
         <v/>
       </c>
       <c r="H18" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I18" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="19">
@@ -925,16 +979,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Lea Neumann</v>
+        <v>Lea Krüger</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D19" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v>✓</v>
+        <v>2.3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="str">
         <v/>
@@ -943,7 +997,10 @@
         <v/>
       </c>
       <c r="H19" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I19" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="20">
@@ -951,16 +1008,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Jonas Hoffmann</v>
+        <v>Jonas Richter</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D20" s="3">
-        <v>3.3</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="str">
         <v/>
@@ -969,7 +1026,10 @@
         <v/>
       </c>
       <c r="H20" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I20" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="21">
@@ -977,7 +1037,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Marie Fischer</v>
+        <v>Marie Schmidt</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>w</v>
@@ -985,8 +1045,8 @@
       <c r="D21" s="3">
         <v>2.3</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+      <c r="E21" s="2">
+        <v>5</v>
       </c>
       <c r="F21" s="2" t="str">
         <v/>
@@ -995,7 +1055,10 @@
         <v/>
       </c>
       <c r="H21" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I21" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="22">
@@ -1003,16 +1066,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Luis Hartmann</v>
+        <v>Luis Wolf</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D22" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="str">
         <v/>
@@ -1021,7 +1084,10 @@
         <v/>
       </c>
       <c r="H22" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v>✓</v>
+      </c>
+      <c r="I22" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="23">
@@ -1029,16 +1095,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Ella Richter</v>
+        <v>Ella Koch</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D23" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1047,6 +1113,9 @@
         <v/>
       </c>
       <c r="H23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I23" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1055,16 +1124,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Emil Neumann</v>
+        <v>Emil Schulz</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="str">
         <v/>
@@ -1073,7 +1142,10 @@
         <v>✓</v>
       </c>
       <c r="H24" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I24" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="25">
@@ -1081,16 +1153,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Leni Koch</v>
+        <v>Leni Klein</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D25" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="str">
         <v/>
@@ -1099,7 +1171,10 @@
         <v/>
       </c>
       <c r="H25" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I25" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="26">
@@ -1107,16 +1182,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Anton Fischer</v>
+        <v>Anton Becker</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D26" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1125,7 +1200,10 @@
         <v/>
       </c>
       <c r="H26" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I26" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="27">
@@ -1133,16 +1211,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Frieda Richter</v>
+        <v>Frieda Schmidt</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D27" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1151,7 +1229,10 @@
         <v/>
       </c>
       <c r="H27" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I27" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="28">
@@ -1159,16 +1240,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Theo Müller</v>
+        <v>Theo Zimmermann</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D28" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
@@ -1177,6 +1258,9 @@
         <v/>
       </c>
       <c r="H28" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="I28" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1185,16 +1269,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Ida Becker</v>
+        <v>Ida Meyer</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D29" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>1.8</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="str">
         <v/>
@@ -1203,6 +1287,9 @@
         <v/>
       </c>
       <c r="H29" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="I29" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1211,24 +1298,27 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Maximilian Wolf</v>
+        <v>Maximilian Braun</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D30" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+        <v>1.6</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
       </c>
       <c r="G30" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H30" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I30" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1237,17 +1327,17 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Lara Müller</v>
+        <v>Lara Wagner</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D31" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="E31" s="2">
         <v>2</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <v/>
-      </c>
       <c r="F31" s="2" t="str">
         <v/>
       </c>
@@ -1255,7 +1345,10 @@
         <v/>
       </c>
       <c r="H31" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I31" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="32">
@@ -1263,16 +1356,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Jakob Becker</v>
+        <v>Jakob Neumann</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D32" s="3">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="str">
         <v>✓</v>
@@ -1281,7 +1374,10 @@
         <v/>
       </c>
       <c r="H32" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I32" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="33">
@@ -1289,25 +1385,28 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Anna Schmidt</v>
+        <v>Anna Hoffmann</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D33" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G33" s="2" t="str">
         <v/>
       </c>
       <c r="H33" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I33" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="34">
@@ -1315,16 +1414,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Moritz Meyer</v>
+        <v>Moritz Klein</v>
       </c>
       <c r="C34" s="2" t="str">
-        <v>m</v>
+        <v>d</v>
       </c>
       <c r="D34" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>4</v>
       </c>
       <c r="F34" s="2" t="str">
         <v/>
@@ -1333,7 +1432,10 @@
         <v/>
       </c>
       <c r="H34" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I34" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="35">
@@ -1341,16 +1443,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Luisa Hartmann</v>
+        <v>Luisa Schulz</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D35" s="3">
-        <v>2</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>2.5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>5</v>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1359,7 +1461,10 @@
         <v/>
       </c>
       <c r="H35" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I35" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="36">
@@ -1367,16 +1472,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Oskar Wolf</v>
+        <v>Oskar Weber</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D36" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="str">
         <v/>
@@ -1385,7 +1490,10 @@
         <v/>
       </c>
       <c r="H36" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I36" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="37">
@@ -1393,25 +1501,28 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Paula Krüger</v>
+        <v>Paula Braun</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D37" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G37" s="2" t="str">
         <v/>
       </c>
       <c r="H37" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I37" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="38">
@@ -1419,16 +1530,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>David Klein</v>
+        <v>David Koch</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D38" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="str">
         <v/>
@@ -1437,6 +1548,9 @@
         <v/>
       </c>
       <c r="H38" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="I38" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1445,16 +1559,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Greta Müller</v>
+        <v>Greta Koch</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D39" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="str">
         <v/>
@@ -1463,7 +1577,10 @@
         <v/>
       </c>
       <c r="H39" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I39" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="40">
@@ -1477,10 +1594,10 @@
         <v>m</v>
       </c>
       <c r="D40" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>1.9</v>
+      </c>
+      <c r="E40" s="2">
+        <v>2</v>
       </c>
       <c r="F40" s="2" t="str">
         <v/>
@@ -1489,7 +1606,10 @@
         <v/>
       </c>
       <c r="H40" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I40" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="41">
@@ -1497,24 +1617,27 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Johanna Zimmermann</v>
+        <v>Johanna Meyer</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D41" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>3.5</v>
+      </c>
+      <c r="E41" s="2">
+        <v>4</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G41" s="2" t="str">
         <v/>
       </c>
       <c r="H41" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I41" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1523,16 +1646,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Lukas Schröder</v>
+        <v>Lukas Koch</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D42" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>1.7</v>
+      </c>
+      <c r="E42" s="2">
+        <v>3</v>
       </c>
       <c r="F42" s="2" t="str">
         <v/>
@@ -1541,7 +1664,10 @@
         <v>✓</v>
       </c>
       <c r="H42" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I42" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="43">
@@ -1555,10 +1681,10 @@
         <v>w</v>
       </c>
       <c r="D43" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E43" s="2">
+        <v>3</v>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1567,7 +1693,10 @@
         <v/>
       </c>
       <c r="H43" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I43" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="44">
@@ -1575,25 +1704,28 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Noah Wagner</v>
+        <v>Noah Meyer</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D44" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+        <v>3.3</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
       </c>
       <c r="G44" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H44" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I44" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="45">
@@ -1601,16 +1733,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Mia Zimmermann</v>
+        <v>Mia Hoffmann</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D45" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4</v>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1619,7 +1751,10 @@
         <v/>
       </c>
       <c r="H45" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I45" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="46">
@@ -1627,25 +1762,28 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Leon Klein</v>
+        <v>Paul Braun</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D46" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
         <v/>
       </c>
       <c r="G46" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H46" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I46" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="47">
@@ -1653,24 +1791,27 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Sophia Koch</v>
+        <v>Sophia Müller</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D47" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G47" s="2" t="str">
         <v/>
       </c>
       <c r="H47" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I47" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1679,16 +1820,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Paul Hoffmann</v>
+        <v>Finn Hoffmann</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D48" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>1.7</v>
+      </c>
+      <c r="E48" s="2">
+        <v>4</v>
       </c>
       <c r="F48" s="2" t="str">
         <v/>
@@ -1697,7 +1838,10 @@
         <v/>
       </c>
       <c r="H48" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I48" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="49">
@@ -1705,16 +1849,16 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Hannah Fischer</v>
+        <v>Hannah Neumann</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D49" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
       </c>
       <c r="F49" s="2" t="str">
         <v/>
@@ -1723,7 +1867,10 @@
         <v/>
       </c>
       <c r="H49" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I49" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="50">
@@ -1731,25 +1878,28 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Ben Koch</v>
+        <v>Elias Hoffmann</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D50" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
       </c>
       <c r="G50" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H50" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v>✓</v>
+      </c>
+      <c r="I50" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="51">
@@ -1757,25 +1907,28 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Lina Wagner</v>
+        <v>Lina Fischer</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D51" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>3.2</v>
+      </c>
+      <c r="E51" s="2">
+        <v>3</v>
       </c>
       <c r="F51" s="2" t="str">
         <v/>
       </c>
       <c r="G51" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H51" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I51" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="52">
@@ -1783,16 +1936,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Finn Koch</v>
+        <v>Felix Schulz</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D52" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
         <v/>
@@ -1801,6 +1954,9 @@
         <v/>
       </c>
       <c r="H52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I52" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1809,24 +1965,27 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Emma Fischer</v>
+        <v>Mila Krüger</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D53" s="3">
-        <v>3</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>2.5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
         <v/>
       </c>
       <c r="G53" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I53" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1835,16 +1994,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Elias Hoffmann</v>
+        <v>Henry Becker</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D54" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2</v>
       </c>
       <c r="F54" s="2" t="str">
         <v/>
@@ -1853,7 +2012,10 @@
         <v/>
       </c>
       <c r="H54" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I54" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="55">
@@ -1861,16 +2023,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Mila Wagner</v>
+        <v>Clara Schröder</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D55" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E55" s="2">
+        <v>3</v>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -1879,6 +2041,9 @@
         <v/>
       </c>
       <c r="H55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I55" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1887,24 +2052,27 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Felix Müller</v>
+        <v>Luis Schneider</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D56" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E56" s="2" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E56" s="2">
+        <v>3</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F56" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G56" s="2" t="str">
-        <v/>
-      </c>
       <c r="H56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I56" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1913,16 +2081,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Clara Krüger</v>
+        <v>Lea Weber</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D57" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="str">
         <v/>
@@ -1931,6 +2099,9 @@
         <v/>
       </c>
       <c r="H57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I57" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1939,16 +2110,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Henry Wagner</v>
+        <v>Emil Schmidt</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D58" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E58" s="2">
+        <v>4</v>
       </c>
       <c r="F58" s="2" t="str">
         <v/>
@@ -1957,6 +2128,9 @@
         <v/>
       </c>
       <c r="H58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I58" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1965,16 +2139,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Lea Koch</v>
+        <v>Marie Neumann</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D59" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>2.5</v>
+      </c>
+      <c r="E59" s="2">
+        <v>3</v>
       </c>
       <c r="F59" s="2" t="str">
         <v/>
@@ -1983,7 +2157,10 @@
         <v/>
       </c>
       <c r="H59" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I59" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="60">
@@ -1991,24 +2168,27 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Jonas Wolf</v>
+        <v>Anton Koch</v>
       </c>
       <c r="C60" s="2" t="str">
-        <v>m</v>
+        <v>d</v>
       </c>
       <c r="D60" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E60" s="2">
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
         <v/>
       </c>
       <c r="G60" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I60" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -2017,16 +2197,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Marie Koch</v>
+        <v>Ella Krüger</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D61" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E61" s="2">
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2035,7 +2215,10 @@
         <v/>
       </c>
       <c r="H61" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I61" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="62">
@@ -2043,25 +2226,28 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Luis Schröder</v>
+        <v>Theo Wolf</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D62" s="3">
-        <v>3</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G62" s="2" t="str">
         <v/>
       </c>
       <c r="H62" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I62" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="63">
@@ -2069,25 +2255,28 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Ella Weber</v>
+        <v>Leni Wolf</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D63" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E63" s="2">
+        <v>4</v>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
       </c>
       <c r="G63" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H63" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I63" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="64">
@@ -2095,7 +2284,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Emil Schulz</v>
+        <v>Maximilian Krüger</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>m</v>
@@ -2103,8 +2292,8 @@
       <c r="D64" s="3">
         <v>2.6</v>
       </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2113,7 +2302,10 @@
         <v/>
       </c>
       <c r="H64" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I64" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="65">
@@ -2121,16 +2313,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Leni Meyer</v>
+        <v>Ida Neumann</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D65" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E65" s="2">
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="str">
         <v/>
@@ -2139,7 +2331,10 @@
         <v/>
       </c>
       <c r="H65" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I65" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="66">
@@ -2147,25 +2342,28 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Anton Schulz</v>
+        <v>Jakob Weber</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D66" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E66" s="2" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2</v>
+      </c>
+      <c r="F66" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F66" s="2" t="str">
-        <v/>
-      </c>
       <c r="G66" s="2" t="str">
         <v/>
       </c>
       <c r="H66" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I66" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="67">
@@ -2173,25 +2371,28 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Frieda Becker</v>
+        <v>Lara Fischer</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D67" s="3">
-        <v>1.6</v>
-      </c>
-      <c r="E67" s="2" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="E67" s="2">
+        <v>3</v>
+      </c>
+      <c r="F67" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G67" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F67" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G67" s="2" t="str">
-        <v/>
-      </c>
       <c r="H67" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I67" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="68">
@@ -2199,16 +2400,16 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Theo Braun</v>
+        <v>Moritz Müller</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D68" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>1.5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2217,7 +2418,10 @@
         <v/>
       </c>
       <c r="H68" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I68" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="69">
@@ -2225,16 +2429,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Ida Weber</v>
+        <v>Anna Meyer</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D69" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2243,6 +2447,9 @@
         <v/>
       </c>
       <c r="H69" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I69" s="2" t="str">
         <v>GS Süd</v>
       </c>
     </row>
@@ -2251,16 +2458,16 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Jakob Klein</v>
+        <v>Oskar Zimmermann</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D70" s="3">
-        <v>3</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v>✓</v>
+        <v>2.6</v>
+      </c>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
         <v/>
@@ -2269,7 +2476,10 @@
         <v/>
       </c>
       <c r="H70" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I70" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="71">
@@ -2277,16 +2487,16 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Lara Wolf</v>
+        <v>Luisa Müller</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D71" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>1.9</v>
+      </c>
+      <c r="E71" s="2">
+        <v>1</v>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2295,7 +2505,10 @@
         <v/>
       </c>
       <c r="H71" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I71" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="72">
@@ -2303,25 +2516,28 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Moritz Müller</v>
+        <v>Julian Meyer</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D72" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E72" s="2">
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="str">
         <v/>
       </c>
       <c r="G72" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H72" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I72" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="73">
@@ -2329,25 +2545,28 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Anna Schulz</v>
+        <v>Paula Schulz</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D73" s="3">
-        <v>3.3</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E73" s="2">
+        <v>3</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G73" s="2" t="str">
         <v/>
       </c>
       <c r="H73" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I73" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="74">
@@ -2355,16 +2574,16 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Oskar Schmidt</v>
+        <v>Lukas Schneider</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D74" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E74" s="2">
+        <v>3</v>
       </c>
       <c r="F74" s="2" t="str">
         <v/>
@@ -2373,7 +2592,10 @@
         <v/>
       </c>
       <c r="H74" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I74" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="75">
@@ -2381,25 +2603,28 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Luisa Klein</v>
+        <v>Greta Fischer</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D75" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G75" s="2" t="str">
         <v/>
       </c>
       <c r="H75" s="2" t="str">
-        <v>GS Süd</v>
+        <v>✓</v>
+      </c>
+      <c r="I75" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="76">
@@ -2407,16 +2632,16 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>David Wagner</v>
+        <v>Leon Schmidt</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D76" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2</v>
       </c>
       <c r="F76" s="2" t="str">
         <v/>
@@ -2425,7 +2650,10 @@
         <v/>
       </c>
       <c r="H76" s="2" t="str">
-        <v>GS Am Park</v>
+        <v>✓</v>
+      </c>
+      <c r="I76" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="77">
@@ -2433,25 +2661,28 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Paula Schulz</v>
+        <v>Johanna Fischer</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D77" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>2.1</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4</v>
       </c>
       <c r="F77" s="2" t="str">
         <v/>
       </c>
       <c r="G77" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H77" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I77" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="78">
@@ -2459,16 +2690,16 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Julian Hoffmann</v>
+        <v>Paul Hartmann</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D78" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2477,7 +2708,10 @@
         <v/>
       </c>
       <c r="H78" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I78" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="79">
@@ -2485,16 +2719,16 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Greta Zimmermann</v>
+        <v>Emilia Schröder</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D79" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3</v>
       </c>
       <c r="F79" s="2" t="str">
         <v/>
@@ -2503,7 +2737,10 @@
         <v/>
       </c>
       <c r="H79" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I79" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="80">
@@ -2511,25 +2748,28 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Lukas Zimmermann</v>
+        <v>Ben Müller</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D80" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E80" s="2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2">
+        <v>3</v>
+      </c>
+      <c r="F80" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F80" s="2" t="str">
-        <v/>
-      </c>
       <c r="G80" s="2" t="str">
         <v/>
       </c>
       <c r="H80" s="2" t="str">
-        <v>GS Süd</v>
+        <v>✓</v>
+      </c>
+      <c r="I80" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="81">
@@ -2537,25 +2777,28 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Emilia Wagner</v>
+        <v>Mia Schmidt</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D81" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G81" s="2" t="str">
         <v/>
       </c>
       <c r="H81" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I81" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="82">
@@ -2563,30 +2806,33 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Noah Schneider</v>
+        <v>Finn Wolf</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D82" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>3.3</v>
+      </c>
+      <c r="E82" s="2">
+        <v>5</v>
       </c>
       <c r="F82" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H82" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="G82" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H82" s="2" t="str">
-        <v>GS Lindenweg</v>
+      <c r="I82" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2597,37 +2843,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C1" s="2">
-        <v>36</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2643,37 +2889,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/de/sample1.xlsx
+++ b/public/samples/de/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Schülerliste" sheetId="2" r:id="rId2"/>
     <sheet name="Zusammen" sheetId="3" r:id="rId3"/>
     <sheet name="Trennen" sheetId="4" r:id="rId4"/>
+    <sheet name="Merkmale" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -663,7 +664,7 @@
         <v>Paul Wagner</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="D8" s="3">
         <v>2.3</v>
@@ -895,7 +896,7 @@
         <v>Felix Schröder</v>
       </c>
       <c r="C16" s="2" t="str">
-        <v>m</v>
+        <v>d</v>
       </c>
       <c r="D16" s="3">
         <v>2.3</v>
@@ -1417,7 +1418,7 @@
         <v>Moritz Klein</v>
       </c>
       <c r="C34" s="2" t="str">
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="D34" s="3">
         <v>3</v>
@@ -1678,7 +1679,7 @@
         <v>Emilia Schneider</v>
       </c>
       <c r="C43" s="2" t="str">
-        <v>w</v>
+        <v>d</v>
       </c>
       <c r="D43" s="3">
         <v>2.2</v>
@@ -2171,7 +2172,7 @@
         <v>Anton Koch</v>
       </c>
       <c r="C60" s="2" t="str">
-        <v>d</v>
+        <v>m</v>
       </c>
       <c r="D60" s="3">
         <v>2.8</v>
@@ -2432,7 +2433,7 @@
         <v>Anna Meyer</v>
       </c>
       <c r="C69" s="2" t="str">
-        <v>w</v>
+        <v>d</v>
       </c>
       <c r="D69" s="3">
         <v>2.3</v>
@@ -2927,4 +2928,103 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Merkmal</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Art</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Optionen</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Geschlecht</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Liste</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>d</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>m</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>w</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Notenschnitt</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Zahl</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Lesekompetenz</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Stufe</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Förderung</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Ankreuzen</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>DaZ</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Ankreuzen</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>Teamfähigkeit</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>Ankreuzen</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>Herkunftsgrundschule</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>Liste</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>GS Am Park</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>GS Lindenweg</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>GS Nord</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>GS Süd</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/de/sample1.xlsx
+++ b/public/samples/de/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Schülerliste" sheetId="2" r:id="rId2"/>
     <sheet name="Zusammen" sheetId="3" r:id="rId3"/>
     <sheet name="Trennen" sheetId="4" r:id="rId4"/>
+    <sheet name="Merkmale" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -450,7 +451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:I82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -477,6 +478,9 @@
       <c r="H1" s="2">
         <v>1</v>
       </c>
+      <c r="I1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -492,15 +496,18 @@
         <v>Notenschnitt</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>Förderbedarf</v>
+        <v>Lesekompetenz</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>Förderung</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>DaZ</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <v>Unterstützung Verhalten</v>
-      </c>
       <c r="H2" s="2" t="str">
+        <v>Teamfähigkeit</v>
+      </c>
+      <c r="I2" s="2" t="str">
         <v>Herkunftsgrundschule</v>
       </c>
     </row>
@@ -517,8 +524,8 @@
       <c r="D3" s="3">
         <v>2.6</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
         <v/>
@@ -527,7 +534,10 @@
         <v/>
       </c>
       <c r="H3" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I3" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="4">
@@ -535,25 +545,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>Noah Schmidt</v>
+        <v>Noah Fischer</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D4" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="E4" s="2" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H4" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G4" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H4" s="2" t="str">
-        <v>GS Lindenweg</v>
+      <c r="I4" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +574,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>Mia Hoffmann</v>
+        <v>Mia Fischer</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D5" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="str">
         <v/>
@@ -579,7 +592,10 @@
         <v/>
       </c>
       <c r="H5" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +603,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>Leon Schröder</v>
+        <v>Leon Hoffmann</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D6" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="str">
         <v/>
@@ -605,7 +621,10 @@
         <v/>
       </c>
       <c r="H6" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I6" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="7">
@@ -613,16 +632,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>Sophia Richter</v>
+        <v>Sophia Klein</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D7" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>2.1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
         <v/>
@@ -631,6 +650,9 @@
         <v/>
       </c>
       <c r="H7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I7" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -639,25 +661,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>Paul Hartmann</v>
+        <v>Paul Wagner</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D8" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="str">
         <v/>
       </c>
       <c r="G8" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H8" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I8" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="9">
@@ -665,16 +690,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>Hannah Richter</v>
+        <v>Hannah Fischer</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D9" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="str">
         <v/>
@@ -683,7 +708,10 @@
         <v/>
       </c>
       <c r="H9" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I9" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="10">
@@ -691,16 +719,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>Ben Müller</v>
+        <v>Ben Hartmann</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D10" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="str">
         <v/>
@@ -709,7 +737,10 @@
         <v/>
       </c>
       <c r="H10" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I10" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="11">
@@ -717,16 +748,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Lina Hartmann</v>
+        <v>Lina Klein</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D11" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="str">
         <v/>
@@ -735,7 +766,10 @@
         <v/>
       </c>
       <c r="H11" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I11" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +777,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>Finn Zimmermann</v>
+        <v>Finn Fischer</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>m</v>
@@ -751,8 +785,8 @@
       <c r="D12" s="3">
         <v>3</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
         <v/>
@@ -761,7 +795,10 @@
         <v/>
       </c>
       <c r="H12" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I12" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="13">
@@ -769,16 +806,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Emma Krüger</v>
+        <v>Emma Neumann</v>
       </c>
       <c r="C13" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D13" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>1.7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
         <v/>
@@ -787,7 +824,10 @@
         <v/>
       </c>
       <c r="H13" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I13" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +835,28 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>Elias Neumann</v>
+        <v>Elias Wolf</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D14" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H14" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="G14" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H14" s="2" t="str">
-        <v>GS Nord</v>
+      <c r="I14" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="15">
@@ -821,25 +864,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>Mila Braun</v>
+        <v>Mila Schmidt</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D15" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v>✓</v>
+        <v>2.4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G15" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H15" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I15" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="16">
@@ -847,16 +893,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>Felix Meyer</v>
+        <v>Felix Schröder</v>
       </c>
       <c r="C16" s="2" t="str">
-        <v>m</v>
+        <v>d</v>
       </c>
       <c r="D16" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
         <v/>
@@ -865,7 +911,10 @@
         <v/>
       </c>
       <c r="H16" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="17">
@@ -873,7 +922,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>Clara Koch</v>
+        <v>Clara Schulz</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>w</v>
@@ -881,17 +930,20 @@
       <c r="D17" s="3">
         <v>3.3</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+      <c r="E17" s="2">
+        <v>4</v>
       </c>
       <c r="F17" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="G17" s="2" t="str">
-        <v/>
-      </c>
       <c r="H17" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I17" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="18">
@@ -899,16 +951,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Henry Richter</v>
+        <v>Henry Hoffmann</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D18" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>3.1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="str">
         <v/>
@@ -917,7 +969,10 @@
         <v/>
       </c>
       <c r="H18" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I18" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="19">
@@ -925,16 +980,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>Lea Neumann</v>
+        <v>Lea Krüger</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D19" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v>✓</v>
+        <v>2.3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="str">
         <v/>
@@ -943,7 +998,10 @@
         <v/>
       </c>
       <c r="H19" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I19" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="20">
@@ -951,16 +1009,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>Jonas Hoffmann</v>
+        <v>Jonas Richter</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D20" s="3">
-        <v>3.3</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="str">
         <v/>
@@ -969,7 +1027,10 @@
         <v/>
       </c>
       <c r="H20" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I20" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="21">
@@ -977,7 +1038,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>Marie Fischer</v>
+        <v>Marie Schmidt</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>w</v>
@@ -985,8 +1046,8 @@
       <c r="D21" s="3">
         <v>2.3</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+      <c r="E21" s="2">
+        <v>5</v>
       </c>
       <c r="F21" s="2" t="str">
         <v/>
@@ -995,7 +1056,10 @@
         <v/>
       </c>
       <c r="H21" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I21" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="22">
@@ -1003,16 +1067,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Luis Hartmann</v>
+        <v>Luis Wolf</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D22" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="str">
         <v/>
@@ -1021,7 +1085,10 @@
         <v/>
       </c>
       <c r="H22" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v>✓</v>
+      </c>
+      <c r="I22" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="23">
@@ -1029,16 +1096,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Ella Richter</v>
+        <v>Ella Koch</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D23" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1047,6 +1114,9 @@
         <v/>
       </c>
       <c r="H23" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I23" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1055,16 +1125,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Emil Neumann</v>
+        <v>Emil Schulz</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="str">
         <v/>
@@ -1073,7 +1143,10 @@
         <v>✓</v>
       </c>
       <c r="H24" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I24" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="25">
@@ -1081,16 +1154,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Leni Koch</v>
+        <v>Leni Klein</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D25" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="str">
         <v/>
@@ -1099,7 +1172,10 @@
         <v/>
       </c>
       <c r="H25" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I25" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="26">
@@ -1107,16 +1183,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Anton Fischer</v>
+        <v>Anton Becker</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D26" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1125,7 +1201,10 @@
         <v/>
       </c>
       <c r="H26" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I26" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="27">
@@ -1133,16 +1212,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Frieda Richter</v>
+        <v>Frieda Schmidt</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D27" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1151,7 +1230,10 @@
         <v/>
       </c>
       <c r="H27" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I27" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="28">
@@ -1159,16 +1241,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Theo Müller</v>
+        <v>Theo Zimmermann</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D28" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
@@ -1177,6 +1259,9 @@
         <v/>
       </c>
       <c r="H28" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="I28" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1185,16 +1270,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Ida Becker</v>
+        <v>Ida Meyer</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D29" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>1.8</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="str">
         <v/>
@@ -1203,6 +1288,9 @@
         <v/>
       </c>
       <c r="H29" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="I29" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1211,24 +1299,27 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Maximilian Wolf</v>
+        <v>Maximilian Braun</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D30" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+        <v>1.6</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
       </c>
       <c r="G30" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H30" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I30" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1237,17 +1328,17 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Lara Müller</v>
+        <v>Lara Wagner</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D31" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="E31" s="2">
         <v>2</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <v/>
-      </c>
       <c r="F31" s="2" t="str">
         <v/>
       </c>
@@ -1255,7 +1346,10 @@
         <v/>
       </c>
       <c r="H31" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I31" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="32">
@@ -1263,16 +1357,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Jakob Becker</v>
+        <v>Jakob Neumann</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D32" s="3">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="str">
         <v>✓</v>
@@ -1281,7 +1375,10 @@
         <v/>
       </c>
       <c r="H32" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I32" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="33">
@@ -1289,25 +1386,28 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Anna Schmidt</v>
+        <v>Anna Hoffmann</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D33" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G33" s="2" t="str">
         <v/>
       </c>
       <c r="H33" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I33" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="34">
@@ -1315,16 +1415,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Moritz Meyer</v>
+        <v>Moritz Klein</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D34" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>4</v>
       </c>
       <c r="F34" s="2" t="str">
         <v/>
@@ -1333,7 +1433,10 @@
         <v/>
       </c>
       <c r="H34" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I34" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="35">
@@ -1341,16 +1444,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Luisa Hartmann</v>
+        <v>Luisa Schulz</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D35" s="3">
-        <v>2</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>2.5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>5</v>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1359,7 +1462,10 @@
         <v/>
       </c>
       <c r="H35" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I35" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="36">
@@ -1367,16 +1473,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Oskar Wolf</v>
+        <v>Oskar Weber</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D36" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="str">
         <v/>
@@ -1385,7 +1491,10 @@
         <v/>
       </c>
       <c r="H36" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I36" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="37">
@@ -1393,25 +1502,28 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Paula Krüger</v>
+        <v>Paula Braun</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D37" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G37" s="2" t="str">
         <v/>
       </c>
       <c r="H37" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I37" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="38">
@@ -1419,16 +1531,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>David Klein</v>
+        <v>David Koch</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D38" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="str">
         <v/>
@@ -1437,6 +1549,9 @@
         <v/>
       </c>
       <c r="H38" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="I38" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1445,16 +1560,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Greta Müller</v>
+        <v>Greta Koch</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D39" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="str">
         <v/>
@@ -1463,7 +1578,10 @@
         <v/>
       </c>
       <c r="H39" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I39" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="40">
@@ -1477,10 +1595,10 @@
         <v>m</v>
       </c>
       <c r="D40" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>1.9</v>
+      </c>
+      <c r="E40" s="2">
+        <v>2</v>
       </c>
       <c r="F40" s="2" t="str">
         <v/>
@@ -1489,7 +1607,10 @@
         <v/>
       </c>
       <c r="H40" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I40" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="41">
@@ -1497,24 +1618,27 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Johanna Zimmermann</v>
+        <v>Johanna Meyer</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D41" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>3.5</v>
+      </c>
+      <c r="E41" s="2">
+        <v>4</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G41" s="2" t="str">
         <v/>
       </c>
       <c r="H41" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I41" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1523,16 +1647,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Lukas Schröder</v>
+        <v>Lukas Koch</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D42" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>1.7</v>
+      </c>
+      <c r="E42" s="2">
+        <v>3</v>
       </c>
       <c r="F42" s="2" t="str">
         <v/>
@@ -1541,7 +1665,10 @@
         <v>✓</v>
       </c>
       <c r="H42" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I42" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="43">
@@ -1552,13 +1679,13 @@
         <v>Emilia Schneider</v>
       </c>
       <c r="C43" s="2" t="str">
-        <v>w</v>
+        <v>d</v>
       </c>
       <c r="D43" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E43" s="2">
+        <v>3</v>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1567,7 +1694,10 @@
         <v/>
       </c>
       <c r="H43" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I43" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="44">
@@ -1575,25 +1705,28 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Noah Wagner</v>
+        <v>Noah Meyer</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D44" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+        <v>3.3</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
       </c>
       <c r="G44" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H44" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I44" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="45">
@@ -1601,16 +1734,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>Mia Zimmermann</v>
+        <v>Mia Hoffmann</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D45" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4</v>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1619,7 +1752,10 @@
         <v/>
       </c>
       <c r="H45" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I45" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="46">
@@ -1627,25 +1763,28 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Leon Klein</v>
+        <v>Paul Braun</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D46" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
         <v/>
       </c>
       <c r="G46" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H46" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I46" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="47">
@@ -1653,24 +1792,27 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Sophia Koch</v>
+        <v>Sophia Müller</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D47" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G47" s="2" t="str">
         <v/>
       </c>
       <c r="H47" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I47" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1679,16 +1821,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Paul Hoffmann</v>
+        <v>Finn Hoffmann</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D48" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>1.7</v>
+      </c>
+      <c r="E48" s="2">
+        <v>4</v>
       </c>
       <c r="F48" s="2" t="str">
         <v/>
@@ -1697,7 +1839,10 @@
         <v/>
       </c>
       <c r="H48" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I48" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="49">
@@ -1705,16 +1850,16 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Hannah Fischer</v>
+        <v>Hannah Neumann</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D49" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
       </c>
       <c r="F49" s="2" t="str">
         <v/>
@@ -1723,7 +1868,10 @@
         <v/>
       </c>
       <c r="H49" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I49" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="50">
@@ -1731,25 +1879,28 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Ben Koch</v>
+        <v>Elias Hoffmann</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D50" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
       </c>
       <c r="G50" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H50" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v>✓</v>
+      </c>
+      <c r="I50" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="51">
@@ -1757,25 +1908,28 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Lina Wagner</v>
+        <v>Lina Fischer</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D51" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>3.2</v>
+      </c>
+      <c r="E51" s="2">
+        <v>3</v>
       </c>
       <c r="F51" s="2" t="str">
         <v/>
       </c>
       <c r="G51" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H51" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I51" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="52">
@@ -1783,16 +1937,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Finn Koch</v>
+        <v>Felix Schulz</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D52" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
         <v/>
@@ -1801,6 +1955,9 @@
         <v/>
       </c>
       <c r="H52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I52" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1809,24 +1966,27 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Emma Fischer</v>
+        <v>Mila Krüger</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D53" s="3">
-        <v>3</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>2.5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
       </c>
       <c r="F53" s="2" t="str">
         <v/>
       </c>
       <c r="G53" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I53" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1835,16 +1995,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Elias Hoffmann</v>
+        <v>Henry Becker</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D54" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2</v>
       </c>
       <c r="F54" s="2" t="str">
         <v/>
@@ -1853,7 +2013,10 @@
         <v/>
       </c>
       <c r="H54" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I54" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="55">
@@ -1861,16 +2024,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Mila Wagner</v>
+        <v>Clara Schröder</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D55" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E55" s="2">
+        <v>3</v>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -1879,6 +2042,9 @@
         <v/>
       </c>
       <c r="H55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I55" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1887,24 +2053,27 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Felix Müller</v>
+        <v>Luis Schneider</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D56" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E56" s="2" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E56" s="2">
+        <v>3</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F56" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G56" s="2" t="str">
-        <v/>
-      </c>
       <c r="H56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I56" s="2" t="str">
         <v>GS Am Park</v>
       </c>
     </row>
@@ -1913,16 +2082,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Clara Krüger</v>
+        <v>Lea Weber</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D57" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="str">
         <v/>
@@ -1931,6 +2100,9 @@
         <v/>
       </c>
       <c r="H57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I57" s="2" t="str">
         <v>GS Nord</v>
       </c>
     </row>
@@ -1939,16 +2111,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Henry Wagner</v>
+        <v>Emil Schmidt</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D58" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="E58" s="2">
+        <v>4</v>
       </c>
       <c r="F58" s="2" t="str">
         <v/>
@@ -1957,6 +2129,9 @@
         <v/>
       </c>
       <c r="H58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I58" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -1965,16 +2140,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Lea Koch</v>
+        <v>Marie Neumann</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D59" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>2.5</v>
+      </c>
+      <c r="E59" s="2">
+        <v>3</v>
       </c>
       <c r="F59" s="2" t="str">
         <v/>
@@ -1983,7 +2158,10 @@
         <v/>
       </c>
       <c r="H59" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I59" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="60">
@@ -1991,24 +2169,27 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Jonas Wolf</v>
+        <v>Anton Koch</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D60" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E60" s="2">
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
         <v/>
       </c>
       <c r="G60" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I60" s="2" t="str">
         <v>GS Lindenweg</v>
       </c>
     </row>
@@ -2017,16 +2198,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Marie Koch</v>
+        <v>Ella Krüger</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D61" s="3">
-        <v>2.2</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>2.8</v>
+      </c>
+      <c r="E61" s="2">
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2035,7 +2216,10 @@
         <v/>
       </c>
       <c r="H61" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I61" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="62">
@@ -2043,25 +2227,28 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Luis Schröder</v>
+        <v>Theo Wolf</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D62" s="3">
-        <v>3</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G62" s="2" t="str">
         <v/>
       </c>
       <c r="H62" s="2" t="str">
-        <v>GS Nord</v>
+        <v/>
+      </c>
+      <c r="I62" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="63">
@@ -2069,25 +2256,28 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Ella Weber</v>
+        <v>Leni Wolf</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D63" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E63" s="2">
+        <v>4</v>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
       </c>
       <c r="G63" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H63" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I63" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="64">
@@ -2095,7 +2285,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Emil Schulz</v>
+        <v>Maximilian Krüger</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>m</v>
@@ -2103,8 +2293,8 @@
       <c r="D64" s="3">
         <v>2.6</v>
       </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2113,7 +2303,10 @@
         <v/>
       </c>
       <c r="H64" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I64" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="65">
@@ -2121,16 +2314,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Leni Meyer</v>
+        <v>Ida Neumann</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D65" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E65" s="2">
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="str">
         <v/>
@@ -2139,7 +2332,10 @@
         <v/>
       </c>
       <c r="H65" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I65" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="66">
@@ -2147,25 +2343,28 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Anton Schulz</v>
+        <v>Jakob Weber</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D66" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E66" s="2" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2</v>
+      </c>
+      <c r="F66" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F66" s="2" t="str">
-        <v/>
-      </c>
       <c r="G66" s="2" t="str">
         <v/>
       </c>
       <c r="H66" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I66" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="67">
@@ -2173,25 +2372,28 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Frieda Becker</v>
+        <v>Lara Fischer</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D67" s="3">
-        <v>1.6</v>
-      </c>
-      <c r="E67" s="2" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="E67" s="2">
+        <v>3</v>
+      </c>
+      <c r="F67" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G67" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F67" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G67" s="2" t="str">
-        <v/>
-      </c>
       <c r="H67" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I67" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="68">
@@ -2199,16 +2401,16 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Theo Braun</v>
+        <v>Moritz Müller</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D68" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>1.5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2217,7 +2419,10 @@
         <v/>
       </c>
       <c r="H68" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I68" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="69">
@@ -2225,16 +2430,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Ida Weber</v>
+        <v>Anna Meyer</v>
       </c>
       <c r="C69" s="2" t="str">
-        <v>w</v>
+        <v>d</v>
       </c>
       <c r="D69" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2243,6 +2448,9 @@
         <v/>
       </c>
       <c r="H69" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I69" s="2" t="str">
         <v>GS Süd</v>
       </c>
     </row>
@@ -2251,16 +2459,16 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Jakob Klein</v>
+        <v>Oskar Zimmermann</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D70" s="3">
-        <v>3</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v>✓</v>
+        <v>2.6</v>
+      </c>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
         <v/>
@@ -2269,7 +2477,10 @@
         <v/>
       </c>
       <c r="H70" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I70" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="71">
@@ -2277,16 +2488,16 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Lara Wolf</v>
+        <v>Luisa Müller</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D71" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>1.9</v>
+      </c>
+      <c r="E71" s="2">
+        <v>1</v>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2295,7 +2506,10 @@
         <v/>
       </c>
       <c r="H71" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I71" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="72">
@@ -2303,25 +2517,28 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Moritz Müller</v>
+        <v>Julian Meyer</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D72" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E72" s="2">
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="str">
         <v/>
       </c>
       <c r="G72" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H72" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I72" s="2" t="str">
+        <v>GS Lindenweg</v>
       </c>
     </row>
     <row r="73">
@@ -2329,25 +2546,28 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Anna Schulz</v>
+        <v>Paula Schulz</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D73" s="3">
-        <v>3.3</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E73" s="2">
+        <v>3</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G73" s="2" t="str">
         <v/>
       </c>
       <c r="H73" s="2" t="str">
-        <v>GS Süd</v>
+        <v/>
+      </c>
+      <c r="I73" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="74">
@@ -2355,16 +2575,16 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Oskar Schmidt</v>
+        <v>Lukas Schneider</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D74" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>2.4</v>
+      </c>
+      <c r="E74" s="2">
+        <v>3</v>
       </c>
       <c r="F74" s="2" t="str">
         <v/>
@@ -2373,7 +2593,10 @@
         <v/>
       </c>
       <c r="H74" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I74" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="75">
@@ -2381,25 +2604,28 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Luisa Klein</v>
+        <v>Greta Fischer</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D75" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G75" s="2" t="str">
         <v/>
       </c>
       <c r="H75" s="2" t="str">
-        <v>GS Süd</v>
+        <v>✓</v>
+      </c>
+      <c r="I75" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="76">
@@ -2407,16 +2633,16 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>David Wagner</v>
+        <v>Leon Schmidt</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D76" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2</v>
       </c>
       <c r="F76" s="2" t="str">
         <v/>
@@ -2425,7 +2651,10 @@
         <v/>
       </c>
       <c r="H76" s="2" t="str">
-        <v>GS Am Park</v>
+        <v>✓</v>
+      </c>
+      <c r="I76" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="77">
@@ -2433,25 +2662,28 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Paula Schulz</v>
+        <v>Johanna Fischer</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D77" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>2.1</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4</v>
       </c>
       <c r="F77" s="2" t="str">
         <v/>
       </c>
       <c r="G77" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H77" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I77" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="78">
@@ -2459,16 +2691,16 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Julian Hoffmann</v>
+        <v>Paul Hartmann</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D78" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>2.7</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2477,7 +2709,10 @@
         <v/>
       </c>
       <c r="H78" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I78" s="2" t="str">
+        <v>GS Nord</v>
       </c>
     </row>
     <row r="79">
@@ -2485,16 +2720,16 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Greta Zimmermann</v>
+        <v>Emilia Schröder</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D79" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>2.3</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3</v>
       </c>
       <c r="F79" s="2" t="str">
         <v/>
@@ -2503,7 +2738,10 @@
         <v/>
       </c>
       <c r="H79" s="2" t="str">
-        <v>GS Lindenweg</v>
+        <v/>
+      </c>
+      <c r="I79" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="80">
@@ -2511,25 +2749,28 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Lukas Zimmermann</v>
+        <v>Ben Müller</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D80" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="E80" s="2" t="str">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2">
+        <v>3</v>
+      </c>
+      <c r="F80" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="F80" s="2" t="str">
-        <v/>
-      </c>
       <c r="G80" s="2" t="str">
         <v/>
       </c>
       <c r="H80" s="2" t="str">
-        <v>GS Süd</v>
+        <v>✓</v>
+      </c>
+      <c r="I80" s="2" t="str">
+        <v>GS Am Park</v>
       </c>
     </row>
     <row r="81">
@@ -2537,25 +2778,28 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Emilia Wagner</v>
+        <v>Mia Schmidt</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>w</v>
       </c>
       <c r="D81" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G81" s="2" t="str">
         <v/>
       </c>
       <c r="H81" s="2" t="str">
-        <v>GS Am Park</v>
+        <v/>
+      </c>
+      <c r="I81" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
     <row r="82">
@@ -2563,30 +2807,33 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Noah Schneider</v>
+        <v>Finn Wolf</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>m</v>
       </c>
       <c r="D82" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>3.3</v>
+      </c>
+      <c r="E82" s="2">
+        <v>5</v>
       </c>
       <c r="F82" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H82" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="G82" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H82" s="2" t="str">
-        <v>GS Lindenweg</v>
+      <c r="I82" s="2" t="str">
+        <v>GS Süd</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2597,37 +2844,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C1" s="2">
-        <v>36</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2643,37 +2890,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2681,4 +2928,103 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Merkmal</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Art</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Optionen</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Geschlecht</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Liste</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>d</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>m</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>w</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Notenschnitt</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Zahl</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Lesekompetenz</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Stufe</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Förderung</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Ankreuzen</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>DaZ</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Ankreuzen</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>Teamfähigkeit</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>Ankreuzen</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>Herkunftsgrundschule</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>Liste</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>GS Am Park</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>GS Lindenweg</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>GS Nord</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>GS Süd</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+  </ignoredErrors>
+</worksheet>
 </file>